--- a/data/Reports/purchase_transcation.xlsx
+++ b/data/Reports/purchase_transcation.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SAKSHI\Downloads\Jaiswal_Group_Report\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SAKSHI\Downloads\Jaiswal_Group_Report\data\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C365386-A2D9-4BC7-A7D7-C6B5C14F17B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EC6A932-BE1D-47F7-8685-74928480551A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="2025" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026'!$C$1:$C$332</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026'!$A$1:$N$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -10393,6 +10393,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:N1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A19:N208">
     <sortCondition descending="1" ref="C1:C208"/>
   </sortState>
